--- a/InputData/indst/_cement/CCF/Calcination CO2 Factor by Pathway.xlsx
+++ b/InputData/indst/_cement/CCF/Calcination CO2 Factor by Pathway.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EEB7CB-4F13-43C1-A518-0CA3BEB66585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D7A59E-6FDA-47A4-8D09-AA9322A92489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>CCF Calcination CO2 Factor by Pathway</t>
   </si>
@@ -78,21 +78,12 @@
     <t>Dry kiln with CCS capture rate</t>
   </si>
   <si>
-    <t>UNVERIFIED - EI judgment; common CCS design-basis capture-rate assumption</t>
-  </si>
-  <si>
     <t>Unmitigated calcination emission factor (EPA GHGI Eq. 4-1)</t>
   </si>
   <si>
     <t>t CO2 / t clinker</t>
   </si>
   <si>
-    <t>g CO2 / t clinker, unrounded</t>
-  </si>
-  <si>
-    <t>g CO2 / t clinker, rounded to nearest 1,000</t>
-  </si>
-  <si>
     <t>Dry kiln with CCS: unmitigated x (1 - capture rate)</t>
   </si>
   <si>
@@ -129,23 +120,45 @@
     <t>Purpose and layout</t>
   </si>
   <si>
-    <t>This file gives the CO2 released by the carbonate chemistry of clinker-making (limestone breaking down into lime and CO2), per metric ton of clinker, for each cement production pathway. The EPS cement module uses it to calculate process emissions, and for the dry kiln with CCS it also uses the gap between this value and the unabated kiln value to size the CO2 the capture unit has to handle. Values are in grams of CO2 per metric ton of clinker.
+    <t>How the values are built</t>
+  </si>
+  <si>
+    <t>Dry kiln with CCS</t>
+  </si>
+  <si>
+    <t>Unit: g CO2/metric ton clinker</t>
+  </si>
+  <si>
+    <t>NETL cement CCS baseline (2023) and DOE-funded US FEED studies (Ste. Genevieve, Mitchell, Balcones): 95% of CO2 in the treated flue gas</t>
+  </si>
+  <si>
+    <t>Capture rate for a cement kiln with CCS</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy, National Energy Technology Laboratory (reviewed by the Portland Cement Association)</t>
+  </si>
+  <si>
+    <t>Analysis of Carbon Capture Retrofits for Cement Plants (DOE/NETL-2023/3856)</t>
+  </si>
+  <si>
+    <t>https://www.netl.doe.gov/projects/files/AnalysisofCarbonCaptureRetrofitsforCementPlants_033123.pdf</t>
+  </si>
+  <si>
+    <t>Base case 95% capture of the CO2 in the treated flue gas (kiln combustion and calcination CO2 together, plus the steam boiler), with a 99% sensitivity. DOE-funded U.S. front-end engineering studies agree: Holcim Ste. Genevieve, Missouri (95% of total emissions), Heidelberg Mitchell, Indiana (95%), and Cemex Balcones, Texas (95%). The older IEAGHG 2013 study assumed 90%.</t>
+  </si>
+  <si>
+    <t>g CO2 / t clinker (value used)</t>
+  </si>
+  <si>
+    <t>The unabated factor is EPA's calcination equation, which gives 0.510 metric tons of CO2 per metric ton of clinker. In grams that is 510,071 per metric ton. The dry kiln with precalciner and the electric kiln both get this full value: switching a kiln from fuel to electricity changes the combustion emissions, not the chemistry of the limestone, and neither pathway captures CO2. Alternative chemistry cement is set to zero, because those binders are made from non-carbonate materials and release no calcination CO2 by design.</t>
+  </si>
+  <si>
+    <t>This file gives the CO2 released by the carbonate chemistry of clinker-making (limestone breaking down into lime and CO2), per metric ton of clinker, for each cement production pathway. The EPS cement module uses it to calculate process emissions, and for the dry kiln with CCS it also reads the capture rate from the gap between this value and the unabated kiln value. The model applies that rate to the calcination CO2 and to the CO2 from burning kiln fuel, to size the CO2 the capture unit has to handle. Values are in grams of CO2 per metric ton of clinker.
 The tabs run from inputs to output. 'Source Data' holds the EPA inputs. 'Parameters' holds the one judgment value you might change, the capture rate for the CCS pathway. 'Calc' does the arithmetic, and the 'CCF' tab reads from it by formula and is what gets exported to CCF.csv.</t>
   </si>
   <si>
-    <t>How the values are built</t>
-  </si>
-  <si>
-    <t>The unabated factor is EPA's calcination equation, which gives 0.510 metric tons of CO2 per metric ton of clinker. We convert it to grams and round to the nearest 1,000 grams, which gives 510,000. The dry kiln with precalciner and the electric kiln both get this full value: switching a kiln from fuel to electricity changes the combustion emissions, not the chemistry of the limestone, and neither pathway captures CO2. Alternative chemistry cement is set to zero, because those binders are made from non-carbonate materials and release no calcination CO2 by design.</t>
-  </si>
-  <si>
-    <t>Dry kiln with CCS</t>
-  </si>
-  <si>
-    <t>The CCS pathway takes the unabated value times one minus the capture rate. We assume the capture unit removes 90% of the calcination CO2, which is a common design-basis figure and our own judgment (no plant-specific figure is used), so the pathway releases 51,000 grams per metric ton. The captured 90% is not lost from the accounting: the CCS sector prices it (capital, operation, transport and storage, energy, and the 45Q tax credit). The energy the capture unit needs is also booked in the CCS sector, not in this file.</t>
-  </si>
-  <si>
-    <t>Unit: g CO2/metric ton clinker</t>
+    <t>The CCS pathway takes the unabated value times one minus the capture rate. We use 95%, the design basis of the NETL baseline and the U.S. engineering studies (range 90-99%), so the pathway releases 25,504 grams per metric ton. The captured 95% is priced in the CCS sector (capital, operation, transport and storage, energy, and the 45Q tax credit), which also books the capture unit's energy.
+Real capture plants treat the whole kiln flue gas, so they capture the CO2 from burning kiln fuel at the same rate as the calcination CO2. The model does the same: it works out the capture rate from this file (the gap between the unabated and CCS values, divided by the unabated value) and applies it to the kiln's fuel CO2 as well, using the fuel use and fuel emission factors already in the model. If you change the capture rate here, the fuel CO2 capture follows automatically.</t>
   </si>
 </sst>
 </file>
@@ -230,10 +243,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,84 +552,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="6">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{32D7BEDE-147F-4965-890D-32A88BC98D80}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{42B0E0B6-9F9A-4BE9-91D2-1E7FD9B637D7}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{89F0C0B8-5B2B-4F3C-B800-61BB96D150F5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -625,18 +670,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -644,7 +689,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -652,7 +697,7 @@
         <v>44.01</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -660,12 +705,12 @@
         <v>56.08</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -673,7 +718,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -689,27 +734,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -720,27 +765,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
       </c>
       <c r="B2">
         <f>'Source Data'!B2*('Source Data'!B3/'Source Data'!B4)</f>
         <v>0.51010164051355211</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -749,27 +794,27 @@
         <v>510101.64051355212</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B4">
-        <f>ROUND(B3,-3)</f>
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <f>(B3)</f>
+        <v>510101.64051355212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <f>B4*(1-Parameters!B3)</f>
-        <v>50999.999999999985</v>
+        <v>25505.082025677628</v>
       </c>
     </row>
   </sheetData>
@@ -783,46 +828,46 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <f>Calc!B4</f>
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>510101.64051355212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <f>Calc!B7</f>
-        <v>50999.999999999985</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25505.082025677628</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <f>Calc!B4</f>
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>510101.64051355212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>

--- a/InputData/indst/_cement/CCF/Calcination CO2 Factor by Pathway.xlsx
+++ b/InputData/indst/_cement/CCF/Calcination CO2 Factor by Pathway.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D7A59E-6FDA-47A4-8D09-AA9322A92489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07DA76E-40B5-484C-87D7-1355B7F6F31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>CCF Calcination CO2 Factor by Pathway</t>
   </si>
@@ -159,6 +159,15 @@
   <si>
     <t>The CCS pathway takes the unabated value times one minus the capture rate. We use 95%, the design basis of the NETL baseline and the U.S. engineering studies (range 90-99%), so the pathway releases 25,504 grams per metric ton. The captured 95% is priced in the CCS sector (capital, operation, transport and storage, energy, and the 45Q tax credit), which also books the capture unit's energy.
 Real capture plants treat the whole kiln flue gas, so they capture the CO2 from burning kiln fuel at the same rate as the calcination CO2. The model does the same: it works out the capture rate from this file (the gap between the unabated and CCS values, divided by the unabated value) and applies it to the kiln's fuel CO2 as well, using the fuel use and fuel emission factors already in the model. If you change the capture rate here, the fuel CO2 capture follows automatically.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln calcination (the same as the dry kiln's) at the CCS pathway's capture rate: the electric kiln's factor times the CCS row over the precalciner row (95 percent captured). Direct separation captures calcination CO2 at 90-99 percent (CemZero 2018; Varnier et al. 2025); the CCS pathway's 95 percent is used.</t>
   </si>
 </sst>
 </file>
@@ -231,7 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -246,8 +255,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -552,21 +567,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -574,67 +589,67 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>2023</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -642,7 +657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -650,12 +665,20 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -670,18 +693,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -689,7 +712,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -697,7 +720,7 @@
         <v>44.01</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -705,12 +728,12 @@
         <v>56.08</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -718,7 +741,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -734,19 +757,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -765,18 +788,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -785,7 +808,7 @@
         <v>0.51010164051355211</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -794,7 +817,7 @@
         <v>510101.64051355212</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -803,12 +826,12 @@
         <v>510101.64051355212</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -827,10 +850,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -838,7 +861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -847,7 +870,7 @@
         <v>510101.64051355212</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -856,7 +879,7 @@
         <v>25505.082025677628</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -865,11 +888,20 @@
         <v>510101.64051355212</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <f>B4*B3/B2</f>
+        <v>25505.082025677628</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>0</v>
       </c>
     </row>
